--- a/forms/trg/Formulir_TRG_f-analysis.xlsx
+++ b/forms/trg/Formulir_TRG_f-analysis.xlsx
@@ -771,7 +771,7 @@
         </is>
       </c>
       <c r="B24" s="7">
-        <f>COUNTA(Anggota!B5:B31)</f>
+        <f>COUNTA(Anggota!B5:B32)</f>
         <v/>
       </c>
     </row>
@@ -782,7 +782,7 @@
         </is>
       </c>
       <c r="B25" s="7">
-        <f>COUNTA(Anggota!F5:F31)</f>
+        <f>COUNTA(Anggota!F5:F32)</f>
         <v/>
       </c>
     </row>
@@ -808,7 +808,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M31"/>
+  <dimension ref="A1:M32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -913,12 +913,12 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>Prof. Dr. Budi Nurwahyu</t>
+          <t>Dr. Muh. Nur., S.Si., M.Si</t>
         </is>
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Leader</t>
         </is>
       </c>
       <c r="D5" s="11" t="inlineStr">
@@ -928,22 +928,18 @@
       </c>
       <c r="E5" s="11" t="inlineStr">
         <is>
-          <t>Fixed Point Theory in Generalized b-metric Spaces</t>
+          <t>Functional Analysis and Fourier Analysis</t>
         </is>
       </c>
       <c r="F5" s="12" t="n"/>
       <c r="G5" s="12" t="n"/>
       <c r="H5" s="12" t="n"/>
       <c r="I5" s="12" t="n"/>
-      <c r="J5" s="11" t="inlineStr">
-        <is>
-          <t>0000-0002-8245-8845</t>
-        </is>
-      </c>
+      <c r="J5" s="12" t="n"/>
       <c r="K5" s="12" t="n"/>
       <c r="L5" s="11" t="inlineStr">
         <is>
-          <t>57194036042</t>
+          <t>57196476123</t>
         </is>
       </c>
       <c r="M5" s="11" t="inlineStr">
@@ -958,12 +954,12 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>Dr. Muhammad Zakir, M.Si</t>
+          <t>Prof. Dr. Budi Nurwahyu</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D6" s="11" t="inlineStr">
@@ -973,7 +969,7 @@
       </c>
       <c r="E6" s="11" t="inlineStr">
         <is>
-          <t>Functional Analysis</t>
+          <t>Fixed Point Theory in Generalized b-metric Spaces</t>
         </is>
       </c>
       <c r="F6" s="12" t="n"/>
@@ -982,13 +978,13 @@
       <c r="I6" s="12" t="n"/>
       <c r="J6" s="11" t="inlineStr">
         <is>
-          <t>0000-0002-1486-0891</t>
+          <t>0000-0002-8245-8845</t>
         </is>
       </c>
       <c r="K6" s="12" t="n"/>
       <c r="L6" s="11" t="inlineStr">
         <is>
-          <t>57479283500</t>
+          <t>57194036042</t>
         </is>
       </c>
       <c r="M6" s="11" t="inlineStr">
@@ -1003,12 +999,12 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>Naimah Aris, S.Si. M.Math</t>
+          <t>Dr. Muhammad Zakir, M.Si</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D7" s="11" t="inlineStr">
@@ -1018,7 +1014,7 @@
       </c>
       <c r="E7" s="11" t="inlineStr">
         <is>
-          <t>Applied Functional Analysis and Partial Differential Equation</t>
+          <t>Functional Analysis</t>
         </is>
       </c>
       <c r="F7" s="12" t="n"/>
@@ -1027,13 +1023,13 @@
       <c r="I7" s="12" t="n"/>
       <c r="J7" s="11" t="inlineStr">
         <is>
-          <t>0000-0002-7465-5371</t>
+          <t>0000-0002-1486-0891</t>
         </is>
       </c>
       <c r="K7" s="12" t="n"/>
       <c r="L7" s="11" t="inlineStr">
         <is>
-          <t>16041346800</t>
+          <t>57479283500</t>
         </is>
       </c>
       <c r="M7" s="11" t="inlineStr">
@@ -1048,12 +1044,12 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>Eliyah Acantha Manapa Sampetoding</t>
+          <t>Naimah Aris, S.Si. M.Math</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D8" s="11" t="inlineStr">
@@ -1063,7 +1059,7 @@
       </c>
       <c r="E8" s="11" t="inlineStr">
         <is>
-          <t>Machine Learning</t>
+          <t>Applied Functional Analysis and Partial Differential Equation</t>
         </is>
       </c>
       <c r="F8" s="12" t="n"/>
@@ -1072,13 +1068,13 @@
       <c r="I8" s="12" t="n"/>
       <c r="J8" s="11" t="inlineStr">
         <is>
-          <t>0009-0003-3594-4888</t>
+          <t>0000-0002-7465-5371</t>
         </is>
       </c>
       <c r="K8" s="12" t="n"/>
       <c r="L8" s="11" t="inlineStr">
         <is>
-          <t>60203495900</t>
+          <t>16041346800</t>
         </is>
       </c>
       <c r="M8" s="11" t="inlineStr">
@@ -1093,12 +1089,12 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>Edy Saputra Rusdi</t>
+          <t>Eliyah Acantha Manapa Sampetoding</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D9" s="11" t="inlineStr">
@@ -1117,13 +1113,13 @@
       <c r="I9" s="12" t="n"/>
       <c r="J9" s="11" t="inlineStr">
         <is>
-          <t>0000-0001-5714-9111</t>
+          <t>0009-0003-3594-4888</t>
         </is>
       </c>
       <c r="K9" s="12" t="n"/>
       <c r="L9" s="11" t="inlineStr">
         <is>
-          <t>57211801688</t>
+          <t>60203495900</t>
         </is>
       </c>
       <c r="M9" s="11" t="inlineStr">
@@ -1138,22 +1134,22 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>Prof. Dr. Sükran Konca</t>
+          <t>Edy Saputra Rusdi</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D10" s="11" t="inlineStr">
         <is>
-          <t>Department of Fundamental Sciences/Mathematics, Faculty of Engineering and Architecture, Izmir Bakircay University, Turkey</t>
+          <t>Hasanuddin University</t>
         </is>
       </c>
       <c r="E10" s="11" t="inlineStr">
         <is>
-          <t>Functional Analysis</t>
+          <t>Machine Learning</t>
         </is>
       </c>
       <c r="F10" s="12" t="n"/>
@@ -1162,13 +1158,13 @@
       <c r="I10" s="12" t="n"/>
       <c r="J10" s="11" t="inlineStr">
         <is>
-          <t>0000-0003-4019-958X</t>
+          <t>0000-0001-5714-9111</t>
         </is>
       </c>
       <c r="K10" s="12" t="n"/>
       <c r="L10" s="11" t="inlineStr">
         <is>
-          <t>55355260500</t>
+          <t>57211801688</t>
         </is>
       </c>
       <c r="M10" s="11" t="inlineStr">
@@ -1183,22 +1179,22 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>Dr. Hemanta Kalita</t>
+          <t>Prof. Dr. Sükran Konca</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D11" s="11" t="inlineStr">
         <is>
-          <t>VIT-Bhopal University, Bhopal-Indore Highway, Sehore, Madhya Pradesh, India</t>
+          <t>Department of Fundamental Sciences/Mathematics, Faculty of Engineering and Architecture, Izmir Bakircay University, Turkey</t>
         </is>
       </c>
       <c r="E11" s="11" t="inlineStr">
         <is>
-          <t>Measure Theory, Function spaces, Integration Theory</t>
+          <t>Functional Analysis</t>
         </is>
       </c>
       <c r="F11" s="12" t="n"/>
@@ -1207,13 +1203,13 @@
       <c r="I11" s="12" t="n"/>
       <c r="J11" s="11" t="inlineStr">
         <is>
-          <t>0000-0002-9798-6608</t>
+          <t>0000-0003-4019-958X</t>
         </is>
       </c>
       <c r="K11" s="12" t="n"/>
       <c r="L11" s="11" t="inlineStr">
         <is>
-          <t>57217859518</t>
+          <t>55355260500</t>
         </is>
       </c>
       <c r="M11" s="11" t="inlineStr">
@@ -1228,22 +1224,22 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>Dr. Al Ashari Masta, S.Si. M.Si</t>
+          <t>Dr. Hemanta Kalita</t>
         </is>
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D12" s="11" t="inlineStr">
         <is>
-          <t>Universitas Pendidikan Indonesia</t>
+          <t>VIT-Bhopal University, Bhopal-Indore Highway, Sehore, Madhya Pradesh, India</t>
         </is>
       </c>
       <c r="E12" s="11" t="inlineStr">
         <is>
-          <t>Mathematics of Analysis</t>
+          <t>Measure Theory, Function spaces, Integration Theory</t>
         </is>
       </c>
       <c r="F12" s="12" t="n"/>
@@ -1252,13 +1248,13 @@
       <c r="I12" s="12" t="n"/>
       <c r="J12" s="11" t="inlineStr">
         <is>
-          <t>0000-0003-2737-3598</t>
+          <t>0000-0002-9798-6608</t>
         </is>
       </c>
       <c r="K12" s="12" t="n"/>
       <c r="L12" s="11" t="inlineStr">
         <is>
-          <t>57189662322</t>
+          <t>57217859518</t>
         </is>
       </c>
       <c r="M12" s="11" t="inlineStr">
@@ -1273,22 +1269,22 @@
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>Dr. Harmanus Batkunde, S.Si M.Si</t>
+          <t>Dr. Al Ashari Masta, S.Si. M.Si</t>
         </is>
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D13" s="11" t="inlineStr">
         <is>
-          <t>Pattimura University</t>
+          <t>Universitas Pendidikan Indonesia</t>
         </is>
       </c>
       <c r="E13" s="11" t="inlineStr">
         <is>
-          <t>Functional Analysis</t>
+          <t>Mathematics of Analysis</t>
         </is>
       </c>
       <c r="F13" s="12" t="n"/>
@@ -1297,13 +1293,13 @@
       <c r="I13" s="12" t="n"/>
       <c r="J13" s="11" t="inlineStr">
         <is>
-          <t>0000-0001-9471-0326</t>
+          <t>0000-0003-2737-3598</t>
         </is>
       </c>
       <c r="K13" s="12" t="n"/>
       <c r="L13" s="11" t="inlineStr">
         <is>
-          <t>57197757314</t>
+          <t>57189662322</t>
         </is>
       </c>
       <c r="M13" s="11" t="inlineStr">
@@ -1318,22 +1314,22 @@
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>Denny Ivanal Hakim, S.Si., M.Si., Ph.D</t>
+          <t>Dr. Harmanus Batkunde, S.Si M.Si</t>
         </is>
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D14" s="11" t="inlineStr">
         <is>
-          <t>Institut Teknologi Bandung</t>
+          <t>Pattimura University</t>
         </is>
       </c>
       <c r="E14" s="11" t="inlineStr">
         <is>
-          <t>Fourier Analysis</t>
+          <t>Functional Analysis</t>
         </is>
       </c>
       <c r="F14" s="12" t="n"/>
@@ -1342,13 +1338,13 @@
       <c r="I14" s="12" t="n"/>
       <c r="J14" s="11" t="inlineStr">
         <is>
-          <t>0000-0001-6560-9368</t>
+          <t>0000-0001-9471-0326</t>
         </is>
       </c>
       <c r="K14" s="12" t="n"/>
       <c r="L14" s="11" t="inlineStr">
         <is>
-          <t>56767956700</t>
+          <t>57197757314</t>
         </is>
       </c>
       <c r="M14" s="11" t="inlineStr">
@@ -1363,31 +1359,39 @@
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>Dr. Mochammad Idris, S.Si., M.Si</t>
+          <t>Denny Ivanal Hakim, S.Si., M.Si., Ph.D</t>
         </is>
       </c>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D15" s="11" t="inlineStr">
         <is>
-          <t>Lambung Mangkurat University</t>
+          <t>Institut Teknologi Bandung</t>
         </is>
       </c>
       <c r="E15" s="11" t="inlineStr">
         <is>
-          <t>Functional Analysis and Fourier Analysis</t>
+          <t>Fourier Analysis</t>
         </is>
       </c>
       <c r="F15" s="12" t="n"/>
       <c r="G15" s="12" t="n"/>
       <c r="H15" s="12" t="n"/>
       <c r="I15" s="12" t="n"/>
-      <c r="J15" s="12" t="n"/>
+      <c r="J15" s="11" t="inlineStr">
+        <is>
+          <t>0000-0001-6560-9368</t>
+        </is>
+      </c>
       <c r="K15" s="12" t="n"/>
-      <c r="L15" s="12" t="n"/>
+      <c r="L15" s="11" t="inlineStr">
+        <is>
+          <t>56767956700</t>
+        </is>
+      </c>
       <c r="M15" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1400,22 +1404,22 @@
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t>Asra Aina, S.Mat., M.Mat</t>
+          <t>Dr. Mochammad Idris, S.Si., M.Si</t>
         </is>
       </c>
       <c r="C16" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D16" s="11" t="inlineStr">
         <is>
-          <t>Hasanuddin University</t>
+          <t>Lambung Mangkurat University</t>
         </is>
       </c>
       <c r="E16" s="11" t="inlineStr">
         <is>
-          <t>Fixed Point</t>
+          <t>Functional Analysis and Fourier Analysis</t>
         </is>
       </c>
       <c r="F16" s="12" t="n"/>
@@ -1437,12 +1441,12 @@
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>Alda Maulida Natsir</t>
+          <t>Asra Aina, S.Mat., M.Mat</t>
         </is>
       </c>
       <c r="C17" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D17" s="11" t="inlineStr">
@@ -1452,7 +1456,7 @@
       </c>
       <c r="E17" s="11" t="inlineStr">
         <is>
-          <t>Graduate</t>
+          <t>Fixed Point</t>
         </is>
       </c>
       <c r="F17" s="12" t="n"/>
@@ -1474,12 +1478,12 @@
       </c>
       <c r="B18" s="11" t="inlineStr">
         <is>
-          <t>Achmad Faisal</t>
+          <t>Alda Maulida Natsir</t>
         </is>
       </c>
       <c r="C18" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D18" s="11" t="inlineStr">
@@ -1489,7 +1493,7 @@
       </c>
       <c r="E18" s="11" t="inlineStr">
         <is>
-          <t>Mathematics</t>
+          <t>Graduate</t>
         </is>
       </c>
       <c r="F18" s="12" t="n"/>
@@ -1511,22 +1515,22 @@
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>Syamsuddin Mas'ud</t>
+          <t>Achmad Faisal</t>
         </is>
       </c>
       <c r="C19" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D19" s="11" t="inlineStr">
         <is>
-          <t>Graduate</t>
+          <t>Hasanuddin University</t>
         </is>
       </c>
       <c r="E19" s="11" t="inlineStr">
         <is>
-          <t>F-Analys Team</t>
+          <t>Mathematics</t>
         </is>
       </c>
       <c r="F19" s="12" t="n"/>
@@ -1546,10 +1550,26 @@
       <c r="A20" s="4" t="n">
         <v>16</v>
       </c>
-      <c r="B20" s="12" t="n"/>
-      <c r="C20" s="12" t="n"/>
-      <c r="D20" s="12" t="n"/>
-      <c r="E20" s="11" t="n"/>
+      <c r="B20" s="11" t="inlineStr">
+        <is>
+          <t>Syamsuddin Mas'ud</t>
+        </is>
+      </c>
+      <c r="C20" s="11" t="inlineStr">
+        <is>
+          <t>Student</t>
+        </is>
+      </c>
+      <c r="D20" s="11" t="inlineStr">
+        <is>
+          <t>Graduate</t>
+        </is>
+      </c>
+      <c r="E20" s="11" t="inlineStr">
+        <is>
+          <t>F-Analys Team</t>
+        </is>
+      </c>
       <c r="F20" s="12" t="n"/>
       <c r="G20" s="12" t="n"/>
       <c r="H20" s="12" t="n"/>
@@ -1557,7 +1577,11 @@
       <c r="J20" s="12" t="n"/>
       <c r="K20" s="12" t="n"/>
       <c r="L20" s="12" t="n"/>
-      <c r="M20" s="12" t="n"/>
+      <c r="M20" s="11" t="inlineStr">
+        <is>
+          <t>Aktif</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="n">
@@ -1746,15 +1770,32 @@
       <c r="L31" s="12" t="n"/>
       <c r="M31" s="12" t="n"/>
     </row>
+    <row r="32">
+      <c r="A32" s="4" t="n">
+        <v>28</v>
+      </c>
+      <c r="B32" s="12" t="n"/>
+      <c r="C32" s="12" t="n"/>
+      <c r="D32" s="12" t="n"/>
+      <c r="E32" s="11" t="n"/>
+      <c r="F32" s="12" t="n"/>
+      <c r="G32" s="12" t="n"/>
+      <c r="H32" s="12" t="n"/>
+      <c r="I32" s="12" t="n"/>
+      <c r="J32" s="12" t="n"/>
+      <c r="K32" s="12" t="n"/>
+      <c r="L32" s="12" t="n"/>
+      <c r="M32" s="12" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:M2"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="F5:H31" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F5:H32" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$A$2:$A$39</formula1>
     </dataValidation>
-    <dataValidation sqref="M5:M31" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="M5:M32" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$C$2:$C$3</formula1>
     </dataValidation>
   </dataValidations>
